--- a/artfynd/A 36471-2021 artfynd.xlsx
+++ b/artfynd/A 36471-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121853549</v>
+        <v>121853557</v>
       </c>
       <c r="B2" t="n">
-        <v>57357</v>
+        <v>74714</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Björsjö/Björsjö kanal, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>604868</v>
+        <v>604996</v>
       </c>
       <c r="R2" t="n">
-        <v>6692319</v>
+        <v>6692421</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -779,7 +774,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>gammal tall</t>
+          <t>björkhögstubbe</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -797,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121853582</v>
+        <v>121853549</v>
       </c>
       <c r="B3" t="n">
-        <v>74706</v>
+        <v>57357</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,38 +804,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6439</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Björsjö/Björsjö kanal, Gstr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>605072</v>
+        <v>604868</v>
       </c>
       <c r="R3" t="n">
-        <v>6692455</v>
+        <v>6692319</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -896,7 +896,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>björkhögstubbe</t>
+          <t>gammal tall</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -914,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121853552</v>
+        <v>121853555</v>
       </c>
       <c r="B4" t="n">
-        <v>90748</v>
+        <v>57373</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,34 +930,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Björsjö/Björsjö kanal, Gstr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>604956</v>
+        <v>604950</v>
       </c>
       <c r="R4" t="n">
-        <v>6692383</v>
+        <v>6692411</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1013,7 +1018,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>äldre tall</t>
+          <t>torrtall</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1031,10 +1036,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121853555</v>
+        <v>121853582</v>
       </c>
       <c r="B5" t="n">
-        <v>57373</v>
+        <v>74706</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1043,43 +1048,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6439</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Björsjö/Björsjö kanal, Gstr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>604950</v>
+        <v>605072</v>
       </c>
       <c r="R5" t="n">
-        <v>6692411</v>
+        <v>6692455</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1135,7 +1135,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>torrtall</t>
+          <t>björkhögstubbe</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1153,10 +1153,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121853581</v>
+        <v>121853552</v>
       </c>
       <c r="B6" t="n">
-        <v>74706</v>
+        <v>90748</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1165,25 +1165,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6439</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>605113</v>
+        <v>604956</v>
       </c>
       <c r="R6" t="n">
-        <v>6692455</v>
+        <v>6692383</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>björkhögstubbe</t>
+          <t>äldre tall</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1270,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121853557</v>
+        <v>121853581</v>
       </c>
       <c r="B7" t="n">
-        <v>74714</v>
+        <v>74706</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1282,25 +1282,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>308</v>
+        <v>6439</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>604996</v>
+        <v>605113</v>
       </c>
       <c r="R7" t="n">
-        <v>6692421</v>
+        <v>6692455</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>

--- a/artfynd/A 36471-2021 artfynd.xlsx
+++ b/artfynd/A 36471-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121853557</v>
+        <v>121853582</v>
       </c>
       <c r="B2" t="n">
-        <v>74714</v>
+        <v>74706</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>308</v>
+        <v>6439</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>604996</v>
+        <v>605072</v>
       </c>
       <c r="R2" t="n">
-        <v>6692421</v>
+        <v>6692455</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121853549</v>
+        <v>121853557</v>
       </c>
       <c r="B3" t="n">
-        <v>57357</v>
+        <v>74714</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,39 +808,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Björsjö/Björsjö kanal, Gstr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>604868</v>
+        <v>604996</v>
       </c>
       <c r="R3" t="n">
-        <v>6692319</v>
+        <v>6692421</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -896,7 +891,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>gammal tall</t>
+          <t>björkhögstubbe</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -914,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121853555</v>
+        <v>121853552</v>
       </c>
       <c r="B4" t="n">
-        <v>57373</v>
+        <v>90748</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,39 +925,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Björsjö/Björsjö kanal, Gstr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>604950</v>
+        <v>604956</v>
       </c>
       <c r="R4" t="n">
-        <v>6692411</v>
+        <v>6692383</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1018,7 +1008,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>torrtall</t>
+          <t>äldre tall</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1036,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121853582</v>
+        <v>121853549</v>
       </c>
       <c r="B5" t="n">
-        <v>74706</v>
+        <v>57357</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1048,38 +1038,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6439</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Björsjö/Björsjö kanal, Gstr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>605072</v>
+        <v>604868</v>
       </c>
       <c r="R5" t="n">
-        <v>6692455</v>
+        <v>6692319</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1135,7 +1130,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>björkhögstubbe</t>
+          <t>gammal tall</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1153,10 +1148,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121853552</v>
+        <v>121853581</v>
       </c>
       <c r="B6" t="n">
-        <v>90748</v>
+        <v>74706</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1165,25 +1160,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>6439</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1193,10 +1188,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>604956</v>
+        <v>605113</v>
       </c>
       <c r="R6" t="n">
-        <v>6692383</v>
+        <v>6692455</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1252,7 +1247,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>äldre tall</t>
+          <t>björkhögstubbe</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1270,10 +1265,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121853581</v>
+        <v>121853555</v>
       </c>
       <c r="B7" t="n">
-        <v>74706</v>
+        <v>57373</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1282,38 +1277,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6439</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Björsjö/Björsjö kanal, Gstr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>605113</v>
+        <v>604950</v>
       </c>
       <c r="R7" t="n">
-        <v>6692455</v>
+        <v>6692411</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>björkhögstubbe</t>
+          <t>torrtall</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>

--- a/artfynd/A 36471-2021 artfynd.xlsx
+++ b/artfynd/A 36471-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121853582</v>
+        <v>121853557</v>
       </c>
       <c r="B2" t="n">
-        <v>74706</v>
+        <v>74714</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6439</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>605072</v>
+        <v>604996</v>
       </c>
       <c r="R2" t="n">
-        <v>6692455</v>
+        <v>6692421</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121853557</v>
+        <v>121853555</v>
       </c>
       <c r="B3" t="n">
-        <v>74714</v>
+        <v>57373</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,34 +808,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>308</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Björsjö/Björsjö kanal, Gstr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>604996</v>
+        <v>604950</v>
       </c>
       <c r="R3" t="n">
-        <v>6692421</v>
+        <v>6692411</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -891,7 +896,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>björkhögstubbe</t>
+          <t>torrtall</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -909,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121853552</v>
+        <v>121853581</v>
       </c>
       <c r="B4" t="n">
-        <v>90748</v>
+        <v>74706</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,25 +926,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>6439</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>604956</v>
+        <v>605113</v>
       </c>
       <c r="R4" t="n">
-        <v>6692383</v>
+        <v>6692455</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1008,7 +1013,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>äldre tall</t>
+          <t>björkhögstubbe</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1148,10 +1153,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121853581</v>
+        <v>121853552</v>
       </c>
       <c r="B6" t="n">
-        <v>74706</v>
+        <v>90748</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1160,25 +1165,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6439</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1188,10 +1193,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>605113</v>
+        <v>604956</v>
       </c>
       <c r="R6" t="n">
-        <v>6692455</v>
+        <v>6692383</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1247,7 +1252,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>björkhögstubbe</t>
+          <t>äldre tall</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1265,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121853555</v>
+        <v>121853582</v>
       </c>
       <c r="B7" t="n">
-        <v>57373</v>
+        <v>74706</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1277,43 +1282,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6439</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Björsjö/Björsjö kanal, Gstr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>604950</v>
+        <v>605072</v>
       </c>
       <c r="R7" t="n">
-        <v>6692411</v>
+        <v>6692455</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>torrtall</t>
+          <t>björkhögstubbe</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>

--- a/artfynd/A 36471-2021 artfynd.xlsx
+++ b/artfynd/A 36471-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121853557</v>
+        <v>121853582</v>
       </c>
       <c r="B2" t="n">
-        <v>74714</v>
+        <v>74706</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>308</v>
+        <v>6439</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>604996</v>
+        <v>605072</v>
       </c>
       <c r="R2" t="n">
-        <v>6692421</v>
+        <v>6692455</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121853555</v>
+        <v>121853549</v>
       </c>
       <c r="B3" t="n">
-        <v>57373</v>
+        <v>57357</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,16 +808,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>604950</v>
+        <v>604868</v>
       </c>
       <c r="R3" t="n">
-        <v>6692411</v>
+        <v>6692319</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -896,7 +896,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>torrtall</t>
+          <t>gammal tall</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -914,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121853581</v>
+        <v>121853557</v>
       </c>
       <c r="B4" t="n">
-        <v>74706</v>
+        <v>74714</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,25 +926,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6439</v>
+        <v>308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>605113</v>
+        <v>604996</v>
       </c>
       <c r="R4" t="n">
-        <v>6692455</v>
+        <v>6692421</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1031,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121853549</v>
+        <v>121853555</v>
       </c>
       <c r="B5" t="n">
-        <v>57357</v>
+        <v>57373</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,16 +1047,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>604868</v>
+        <v>604950</v>
       </c>
       <c r="R5" t="n">
-        <v>6692319</v>
+        <v>6692411</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1135,7 +1135,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>gammal tall</t>
+          <t>torrtall</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1270,7 +1270,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121853582</v>
+        <v>121853581</v>
       </c>
       <c r="B7" t="n">
         <v>74706</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>605072</v>
+        <v>605113</v>
       </c>
       <c r="R7" t="n">
         <v>6692455</v>

--- a/artfynd/A 36471-2021 artfynd.xlsx
+++ b/artfynd/A 36471-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121853552</v>
+        <v>121853555</v>
       </c>
       <c r="B2" t="n">
-        <v>90799</v>
+        <v>57390</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Björsjö/Björsjö kanal, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>604956</v>
+        <v>604950</v>
       </c>
       <c r="R2" t="n">
-        <v>6692383</v>
+        <v>6692411</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -774,7 +779,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>äldre tall</t>
+          <t>torrtall</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -792,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121853557</v>
+        <v>121853582</v>
       </c>
       <c r="B3" t="n">
-        <v>74739</v>
+        <v>74731</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,25 +809,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>308</v>
+        <v>6439</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>604996</v>
+        <v>605072</v>
       </c>
       <c r="R3" t="n">
-        <v>6692421</v>
+        <v>6692455</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -1026,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121853582</v>
+        <v>121853552</v>
       </c>
       <c r="B5" t="n">
-        <v>74731</v>
+        <v>90799</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,25 +1043,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6439</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1071,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>605072</v>
+        <v>604956</v>
       </c>
       <c r="R5" t="n">
-        <v>6692455</v>
+        <v>6692383</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1125,7 +1130,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>björkhögstubbe</t>
+          <t>äldre tall</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1143,10 +1148,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121853555</v>
+        <v>121853557</v>
       </c>
       <c r="B6" t="n">
-        <v>57390</v>
+        <v>74739</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,39 +1164,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Björsjö/Björsjö kanal, Gstr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>604950</v>
+        <v>604996</v>
       </c>
       <c r="R6" t="n">
-        <v>6692411</v>
+        <v>6692421</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1247,7 +1247,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>torrtall</t>
+          <t>björkhögstubbe</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>

--- a/artfynd/A 36471-2021 artfynd.xlsx
+++ b/artfynd/A 36471-2021 artfynd.xlsx
@@ -1268,7 +1268,7 @@
         <v>121853549</v>
       </c>
       <c r="B7" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 36471-2021 artfynd.xlsx
+++ b/artfynd/A 36471-2021 artfynd.xlsx
@@ -1283,11 +1283,6 @@
       <c r="E7" t="n">
         <v>100109</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>

--- a/artfynd/A 36471-2021 artfynd.xlsx
+++ b/artfynd/A 36471-2021 artfynd.xlsx
@@ -1268,7 +1268,7 @@
         <v>121853549</v>
       </c>
       <c r="B7" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1282,6 +1282,11 @@
       </c>
       <c r="E7" t="n">
         <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>

--- a/artfynd/A 36471-2021 artfynd.xlsx
+++ b/artfynd/A 36471-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121853555</v>
+        <v>121853557</v>
       </c>
       <c r="B2" t="n">
-        <v>57390</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Björsjö/Björsjö kanal, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>604950</v>
+        <v>604996</v>
       </c>
       <c r="R2" t="n">
-        <v>6692411</v>
+        <v>6692421</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -779,7 +769,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>torrtall</t>
+          <t>björkhögstubbe</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -797,37 +787,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121853582</v>
+        <v>121853552</v>
       </c>
       <c r="B3" t="n">
-        <v>74731</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6439</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>605072</v>
+        <v>604956</v>
       </c>
       <c r="R3" t="n">
-        <v>6692455</v>
+        <v>6692383</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -896,7 +881,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>björkhögstubbe</t>
+          <t>äldre tall</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -914,37 +899,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121853581</v>
+        <v>121853562</v>
       </c>
       <c r="B4" t="n">
-        <v>74731</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6439</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -954,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>605113</v>
+        <v>604522</v>
       </c>
       <c r="R4" t="n">
-        <v>6692455</v>
+        <v>6691888</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1008,12 +988,12 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>blandskog på starkt dikespåverkad mark</t>
+          <t>äldre talldominerad skog i anslutning till sjö</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>björkhögstubbe</t>
+          <t>äldre tall</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1031,37 +1011,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121853552</v>
+        <v>121853581</v>
       </c>
       <c r="B5" t="n">
-        <v>90799</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>6439</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1071,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>604956</v>
+        <v>605113</v>
       </c>
       <c r="R5" t="n">
-        <v>6692383</v>
+        <v>6692455</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1130,7 +1105,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>äldre tall</t>
+          <t>björkhögstubbe</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1148,37 +1123,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121853557</v>
+        <v>121853582</v>
       </c>
       <c r="B6" t="n">
-        <v>74739</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>308</v>
+        <v>6439</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1188,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>604996</v>
+        <v>605072</v>
       </c>
       <c r="R6" t="n">
-        <v>6692421</v>
+        <v>6692455</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1265,32 +1235,27 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121853549</v>
+        <v>121853555</v>
       </c>
       <c r="B7" t="n">
-        <v>57383</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1310,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>604868</v>
+        <v>604950</v>
       </c>
       <c r="R7" t="n">
-        <v>6692319</v>
+        <v>6692411</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1369,7 +1334,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>gammal tall</t>
+          <t>torrtall</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1384,6 +1349,474 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>121853549</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Björsjö/Björsjö kanal, Gstr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>604868</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6692319</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hedesunda</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-05-06</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-05-06</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Gysinge Skog naturvärdesbedömning.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>blandskog på starkt dikespåverkad mark</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>gammal tall</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>121853569</v>
+      </c>
+      <c r="B9" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Björsjö/Björsjö kanal, Gstr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>604710</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6692062</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hedesunda</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-05-06</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-05-06</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Gysinge Skog naturvärdesbedömning.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>äldre barrblandskog</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>torrgran</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>121853560</v>
+      </c>
+      <c r="B10" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Björsjö/Björsjö kanal, Gstr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>604610</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6691997</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hedesunda</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-05-06</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-05-06</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Gysinge Skog naturvärdesbedömning.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>äldre barrblandskog</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>121853541</v>
+      </c>
+      <c r="B11" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Björsjö/Björsjö kanal, Gstr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>604716</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6692241</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hedesunda</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-05-06</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-05-06</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Gysinge Skog naturvärdesbedömning.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>blandskog på starkt dikespåverkad mark</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>björkhögstubbe</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
